--- a/templates/입력서식_템플릿.xlsx
+++ b/templates/입력서식_템플릿.xlsx
@@ -595,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -630,29 +630,33 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>공사명</t>
+          <t>사업명</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr"/>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>보고서 표지·머리글에 사용</t>
+          <t>보고서 표지(비우면 공사명)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>발주청</t>
+          <t>공사명</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr"/>
-      <c r="C4" s="6" t="inlineStr"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>보고서 표지·머리글에 사용</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>사업위치</t>
+          <t>발주청</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr"/>
@@ -661,775 +665,810 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>시설유형(부록5)</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>기타건축물</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>부록5 산정공식 유형 (해당없음 가능)</t>
-        </is>
-      </c>
+          <t>사업위치</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr"/>
+      <c r="C6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>총공사비(백만원)</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n">
-        <v>0</v>
-      </c>
+          <t>시설구분</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr"/>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>추정금액(추정가격+부가세+관급자재비)</t>
+          <t>시설 구분(공공하수처리시설·공공폐수처리시설·하수관로 등) — 보고서 사업개요</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>착공예정일</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n">
-        <v>46143</v>
+          <t>시설유형(부록5)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>기타건축물</t>
+        </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD</t>
+          <t>부록5 산정공식 유형 (해당없음 가능)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>■ 준비·정리기간 (비작업일수 미계상)</t>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>총공사비(백만원)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>추정금액(추정가격+부가세+관급자재비)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>준비기간 공사유형</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>상수도공사</t>
-        </is>
+          <t>착공예정일</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>46143</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>가이드라인 준비기간 예시 유형</t>
+          <t>YYYY-MM-DD</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>준비기간(일)</t>
+          <t>준공예정일</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>비우면 공사유형 예시값 적용</t>
+          <t>YYYY-MM-DD — 목표기간 기준 '준공예정일'일 때 목표 공사기간</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>준비기간 산정사유</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr"/>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>보고서 문구</t>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>■ 준비·정리기간 (비작업일수 미계상)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>정리기간(일)</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n">
-        <v>30</v>
+          <t>준비기간 공사유형</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>상수도공사</t>
+        </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>준공 전 1개월 범위</t>
+          <t>가이드라인 준비기간 예시 유형</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>■ 비작업일수 조건</t>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>준비기간(일)</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>비우면 공사유형 예시값 적용</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>기상관측지점</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>서울</t>
-        </is>
-      </c>
+          <t>준비기간 산정사유</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr"/>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>부록3 95개 관측지점 중 선택(최인접 행정지역)</t>
+          <t>보고서 문구</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>비작업일수 정수반올림</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+          <t>정리기간(일)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>30</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>월별 비작업일수 소수점 첫째자리 반올림</t>
+          <t>준공 전 1개월 범위</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>주40시간 하한(일/월)</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>가이드라인: 월 8일</t>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>■ 비작업일수 조건</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>동절기 공사중지</t>
+          <t>기상관측지점</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>추가검토</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>미반영 / 반영 / 추가검토(미반영 기준 산정 + 반영 시 별도 검토)</t>
+          <t>부록3 95개 관측지점 중 선택(최인접 행정지역)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>동절기 중지월</t>
+          <t>비작업일수 정수반올림</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>12,1,2</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>쉼표 구분</t>
+          <t>월별 비작업일수 소수점 첫째자리 반올림</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>준비·정리기간 동절기 중지</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+          <t>주40시간 하한(일/월)</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Y: 동절기에는 준비·정리기간도 진행하지 않음 / N: 동절기 중에도 준비·정리 진행</t>
+          <t>가이드라인: 월 8일</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>■ 작업일수 보정 (부록4 1일작업량에 곱하는 계수)</t>
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>동절기 공사중지</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>추가검토</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>미반영 / 반영 / 추가검토(미반영 기준 산정 + 반영 시 별도 검토)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>현장여건</t>
+          <t>동절기 중지월</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr"/>
+          <t>12,1,2</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>쉼표 구분</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>공사규모</t>
+          <t>준비·정리기간 동절기 중지</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Y: 동절기에는 준비·정리기간도 진행하지 않음 / N: 동절기 중에도 준비·정리 진행</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>지질조건</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>양호(토사)</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>지반 관련 공종에만 적용</t>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>■ 작업일수 보정 (부록4 1일작업량에 곱하는 계수)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>기상기후</t>
+          <t>현장여건</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>일반</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>옥외·구조물 공정에만 적용</t>
-        </is>
-      </c>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>작업일수 산정단위(일)</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>단위작업 작업일수 올림 단위: 1(1일 미만은 1일, 샘플보고서) 또는 0.1(검토엑셀)</t>
-        </is>
-      </c>
+          <t>공사규모</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>작업조 최대배수</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="n">
-        <v>2</v>
+          <t>지질조건</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>양호(토사)</t>
+        </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>공기조정 시 단위작업 작업조 상한 = 작업조 × 배수</t>
+          <t>지반 관련 공종에만 적용</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>공사여건 보정일수</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="n">
-        <v>0</v>
+          <t>기상기후</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>제2장 2.(6) 공사여건 등에 따른 추가 공사기간(일)</t>
+          <t>옥외·구조물 공정에만 적용</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>공사여건 보정사유</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr"/>
-      <c r="C29" s="6" t="inlineStr"/>
+          <t>작업일수 산정단위(일)</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>단위작업 작업일수 올림 단위: 1(1일 미만은 1일, 샘플보고서) 또는 0.1(검토엑셀)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>■ 목표기간 및 공기조정</t>
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>작업조 최대배수</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>공기조정 시 단위작업 작업조 상한 = 작업조 × 배수</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>목표기간 기준</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
+          <t>공사여건 보정일수</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>없음 / 발주처요구 / 건설사업관리기간</t>
+          <t>제2장 2.(6) 공사여건 등에 따른 추가 공사기간(일)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>발주처 요구 공사기간(개월)</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="n"/>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>목표기간 기준이 '발주처요구'일 때</t>
-        </is>
-      </c>
+          <t>공사여건 보정사유</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr"/>
+      <c r="C32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>공기조정 결과 채택</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>목표 초과 시 조정안을 최종 공사기간으로 채택</t>
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>■ 목표기간 및 공기조정</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>■ 적정성 검토 변수</t>
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>목표기간 기준</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>없음 / 발주처요구 / 건설사업관리기간 / 준공예정일</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>허용범위(±)</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="n">
-        <v>0.2</v>
-      </c>
+          <t>발주처 요구 공사기간(개월)</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n"/>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>가이드라인 ±20%</t>
+          <t>목표기간 기준이 '발주처요구'일 때</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>적정성 판정기준</t>
+          <t>공기조정 결과 채택</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>자동</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>자동(부록5·동종실적 중 하나 이상 충족) / 부록5 / 동종공사 / 모두</t>
+          <t>목표 초과 시 조정안을 최종 공사기간으로 채택</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>연면적(100㎡)</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="n"/>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>A — 기타건축물</t>
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>■ 적정성 검토 변수</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>지상층수</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="n"/>
+          <t>허용범위(±)</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>0.2</v>
+      </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>G — 기타건축물·공동주택</t>
+          <t>가이드라인 ±20%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>지하층수</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="n"/>
+          <t>적정성 판정기준</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>자동</t>
+        </is>
+      </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>B — 기타건축물</t>
+          <t>자동(부록5·동종실적 중 하나 이상 충족) / 부록5 / 동종공사 / 모두</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>도로연장(m)</t>
+          <t>연면적(100㎡)</t>
         </is>
       </c>
       <c r="B40" s="7" t="n"/>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>L — 도로포장·도로</t>
+          <t>A — 기타건축물</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>도로폭원(m)</t>
+          <t>지상층수</t>
         </is>
       </c>
       <c r="B41" s="7" t="n"/>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>W — 도로(토공+교량)</t>
+          <t>G — 기타건축물·공동주택</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>교량연장(m)</t>
+          <t>지하층수</t>
         </is>
       </c>
       <c r="B42" s="7" t="n"/>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>BL — 도로(토공+교량)</t>
+          <t>B — 기타건축물</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>관경(mm)</t>
+          <t>도로연장(m)</t>
         </is>
       </c>
       <c r="B43" s="7" t="n"/>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>D — 상수도</t>
+          <t>L — 도로포장·도로</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>양수·배수·가압장 개수</t>
+          <t>도로폭원(m)</t>
         </is>
       </c>
       <c r="B44" s="7" t="n"/>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>S — 상수도</t>
+          <t>W — 도로(토공+교량)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>하수도연장(m)</t>
+          <t>교량연장(m)</t>
         </is>
       </c>
       <c r="B45" s="7" t="n"/>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>SL — 하수도</t>
+          <t>BL — 도로(토공+교량)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>궤도연장(m)</t>
+          <t>관경(mm)</t>
         </is>
       </c>
       <c r="B46" s="7" t="n"/>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>RL — 철도(궤도)</t>
+          <t>D — 상수도</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>시설용량(㎥/일)</t>
+          <t>양수·배수·가압장 개수</t>
         </is>
       </c>
       <c r="B47" s="7" t="n"/>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>V — 환경공단 산정식</t>
+          <t>S — 상수도</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>환경공단 산정식</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
+          <t>하수도연장(m)</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="n"/>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>환경시설 참고기준</t>
+          <t>SL — 하수도</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>환경공단 경험치</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
+          <t>궤도연장(m)</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="n"/>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>참고기준</t>
+          <t>RL — 철도(궤도)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>유사사례 준비·정리 가산</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>시설용량(㎥/일)</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="n"/>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>가이드라인: 실적평균 + 준비·정리기간</t>
+          <t>V — 환경공단 산정식</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>■ 보고서 서술 (비우면 자동문구)</t>
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>환경공단 산정식</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>환경시설 참고기준</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>사업목적</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="inlineStr"/>
+          <t>환경공단 경험치</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>제1장 1.1</t>
+          <t>참고기준</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>사업내용</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr"/>
+          <t>유사사례 준비·정리 가산</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>제1장 1.2 (줄바꿈으로 항목 구분)</t>
+          <t>가이드라인: 실적평균 + 준비·정리기간</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>추진경위</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr"/>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>제1장 (줄바꿈 구분)</t>
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>■ 보고서 서술 (비우면 자동문구)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>공사특성</t>
+          <t>사업목적</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr"/>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>제2장 2.2.1 (줄바꿈 구분)</t>
+          <t>제1장 1.1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>시공조건 및 지연요인</t>
+          <t>사업내용</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr"/>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>제2장 기타 공사기간 지연사항</t>
+          <t>제1장 1.2 (줄바꿈으로 항목 구분)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>검토자</t>
+          <t>추진경위</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr"/>
       <c r="C57" s="6" t="inlineStr">
         <is>
+          <t>제1장 (줄바꿈 구분)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>공사특성</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr"/>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>제2장 2.2.1 (줄바꿈 구분)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>시공조건 및 지연요인</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr"/>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>제2장 기타 공사기간 지연사항</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>검토자</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr"/>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
           <t>보고서 표지</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A51:C51"/>
   </mergeCells>
   <dataValidations count="17">
-    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"학교,청사,의료시설,경찰서,대학·연구시설,공연·전시시설,기숙사,공장·창고,체육시설(300억이하),소방시설,공동주택,체육시설(10억이상),기타건축물,도로포장,도로(토공+교량),농업용수,상수도,하수도,철도(궤도),해당없음"</formula1>
     </dataValidation>
-    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"공동주택,고속도로공사,철도공사,포장공사(신설),포장공사(수선),공동구공사,상수도공사,하천공사,항만공사,강교가설공사,PC교량공사,교량보수공사,직접입력"</formula1>
     </dataValidation>
-    <dataValidation sqref="B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=_목록!$A$1:$A$95</formula1>
     </dataValidation>
-    <dataValidation sqref="B16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"미반영,반영,추가검토"</formula1>
     </dataValidation>
-    <dataValidation sqref="B20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="B22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"양호,보통,협소·도심지,운영중 시설 내 공사"</formula1>
     </dataValidation>
-    <dataValidation sqref="B23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"대규모,보통,소규모"</formula1>
     </dataValidation>
-    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"양호(토사),풍화암 혼재,연암 이상,연약지반"</formula1>
     </dataValidation>
-    <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"일반,한랭지,다우·해안강풍"</formula1>
     </dataValidation>
-    <dataValidation sqref="B26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,0.1"</formula1>
     </dataValidation>
-    <dataValidation sqref="B31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"없음,발주처요구,건설사업관리기간"</formula1>
+    <dataValidation sqref="B34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"없음,발주처요구,건설사업관리기간,준공예정일"</formula1>
     </dataValidation>
-    <dataValidation sqref="B33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"자동,부록5,동종공사,모두"</formula1>
     </dataValidation>
-    <dataValidation sqref="B48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"폐수처리시설,해당없음"</formula1>
     </dataValidation>
-    <dataValidation sqref="B49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"처리장,하수관로,해당없음"</formula1>
     </dataValidation>
-    <dataValidation sqref="B50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3713,7 +3752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3727,6 +3766,8 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3783,6 +3824,16 @@
       <c r="K1" s="4" t="inlineStr">
         <is>
           <t>비고</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>착수가능일</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>소속공사</t>
         </is>
       </c>
     </row>
@@ -3798,6 +3849,8 @@
       <c r="I2" s="11" t="n"/>
       <c r="J2" s="11" t="n"/>
       <c r="K2" s="11" t="n"/>
+      <c r="L2" s="11" t="n"/>
+      <c r="M2" s="11" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n"/>
@@ -3811,6 +3864,8 @@
       <c r="I3" s="11" t="n"/>
       <c r="J3" s="11" t="n"/>
       <c r="K3" s="11" t="n"/>
+      <c r="L3" s="11" t="n"/>
+      <c r="M3" s="11" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n"/>
@@ -3824,6 +3879,8 @@
       <c r="I4" s="11" t="n"/>
       <c r="J4" s="11" t="n"/>
       <c r="K4" s="11" t="n"/>
+      <c r="L4" s="11" t="n"/>
+      <c r="M4" s="11" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n"/>
@@ -3837,6 +3894,8 @@
       <c r="I5" s="11" t="n"/>
       <c r="J5" s="11" t="n"/>
       <c r="K5" s="11" t="n"/>
+      <c r="L5" s="11" t="n"/>
+      <c r="M5" s="11" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n"/>
@@ -3850,6 +3909,8 @@
       <c r="I6" s="11" t="n"/>
       <c r="J6" s="11" t="n"/>
       <c r="K6" s="11" t="n"/>
+      <c r="L6" s="11" t="n"/>
+      <c r="M6" s="11" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n"/>
@@ -3863,6 +3924,8 @@
       <c r="I7" s="11" t="n"/>
       <c r="J7" s="11" t="n"/>
       <c r="K7" s="11" t="n"/>
+      <c r="L7" s="11" t="n"/>
+      <c r="M7" s="11" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n"/>
@@ -3876,6 +3939,8 @@
       <c r="I8" s="11" t="n"/>
       <c r="J8" s="11" t="n"/>
       <c r="K8" s="11" t="n"/>
+      <c r="L8" s="11" t="n"/>
+      <c r="M8" s="11" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n"/>
@@ -3889,6 +3954,8 @@
       <c r="I9" s="11" t="n"/>
       <c r="J9" s="11" t="n"/>
       <c r="K9" s="11" t="n"/>
+      <c r="L9" s="11" t="n"/>
+      <c r="M9" s="11" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="n"/>
@@ -3902,6 +3969,8 @@
       <c r="I10" s="11" t="n"/>
       <c r="J10" s="11" t="n"/>
       <c r="K10" s="11" t="n"/>
+      <c r="L10" s="11" t="n"/>
+      <c r="M10" s="11" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="n"/>
@@ -3915,6 +3984,8 @@
       <c r="I11" s="11" t="n"/>
       <c r="J11" s="11" t="n"/>
       <c r="K11" s="11" t="n"/>
+      <c r="L11" s="11" t="n"/>
+      <c r="M11" s="11" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n"/>
@@ -3928,6 +3999,8 @@
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="11" t="n"/>
       <c r="K12" s="11" t="n"/>
+      <c r="L12" s="11" t="n"/>
+      <c r="M12" s="11" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n"/>
@@ -3941,6 +4014,8 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="11" t="n"/>
       <c r="K13" s="11" t="n"/>
+      <c r="L13" s="11" t="n"/>
+      <c r="M13" s="11" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="n"/>
@@ -3954,6 +4029,8 @@
       <c r="I14" s="11" t="n"/>
       <c r="J14" s="11" t="n"/>
       <c r="K14" s="11" t="n"/>
+      <c r="L14" s="11" t="n"/>
+      <c r="M14" s="11" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="n"/>
@@ -3967,6 +4044,8 @@
       <c r="I15" s="11" t="n"/>
       <c r="J15" s="11" t="n"/>
       <c r="K15" s="11" t="n"/>
+      <c r="L15" s="11" t="n"/>
+      <c r="M15" s="11" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="n"/>
@@ -3980,6 +4059,8 @@
       <c r="I16" s="11" t="n"/>
       <c r="J16" s="11" t="n"/>
       <c r="K16" s="11" t="n"/>
+      <c r="L16" s="11" t="n"/>
+      <c r="M16" s="11" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="n"/>
@@ -3993,6 +4074,8 @@
       <c r="I17" s="11" t="n"/>
       <c r="J17" s="11" t="n"/>
       <c r="K17" s="11" t="n"/>
+      <c r="L17" s="11" t="n"/>
+      <c r="M17" s="11" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="n"/>
@@ -4006,6 +4089,8 @@
       <c r="I18" s="11" t="n"/>
       <c r="J18" s="11" t="n"/>
       <c r="K18" s="11" t="n"/>
+      <c r="L18" s="11" t="n"/>
+      <c r="M18" s="11" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="n"/>
@@ -4019,6 +4104,8 @@
       <c r="I19" s="11" t="n"/>
       <c r="J19" s="11" t="n"/>
       <c r="K19" s="11" t="n"/>
+      <c r="L19" s="11" t="n"/>
+      <c r="M19" s="11" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="n"/>
@@ -4032,6 +4119,8 @@
       <c r="I20" s="11" t="n"/>
       <c r="J20" s="11" t="n"/>
       <c r="K20" s="11" t="n"/>
+      <c r="L20" s="11" t="n"/>
+      <c r="M20" s="11" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="n"/>
@@ -4045,6 +4134,8 @@
       <c r="I21" s="11" t="n"/>
       <c r="J21" s="11" t="n"/>
       <c r="K21" s="11" t="n"/>
+      <c r="L21" s="11" t="n"/>
+      <c r="M21" s="11" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="n"/>
@@ -4058,6 +4149,8 @@
       <c r="I22" s="11" t="n"/>
       <c r="J22" s="11" t="n"/>
       <c r="K22" s="11" t="n"/>
+      <c r="L22" s="11" t="n"/>
+      <c r="M22" s="11" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="n"/>
@@ -4071,6 +4164,8 @@
       <c r="I23" s="11" t="n"/>
       <c r="J23" s="11" t="n"/>
       <c r="K23" s="11" t="n"/>
+      <c r="L23" s="11" t="n"/>
+      <c r="M23" s="11" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="n"/>
@@ -4084,6 +4179,8 @@
       <c r="I24" s="11" t="n"/>
       <c r="J24" s="11" t="n"/>
       <c r="K24" s="11" t="n"/>
+      <c r="L24" s="11" t="n"/>
+      <c r="M24" s="11" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="n"/>
@@ -4097,6 +4194,8 @@
       <c r="I25" s="11" t="n"/>
       <c r="J25" s="11" t="n"/>
       <c r="K25" s="11" t="n"/>
+      <c r="L25" s="11" t="n"/>
+      <c r="M25" s="11" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="n"/>
@@ -4110,6 +4209,8 @@
       <c r="I26" s="11" t="n"/>
       <c r="J26" s="11" t="n"/>
       <c r="K26" s="11" t="n"/>
+      <c r="L26" s="11" t="n"/>
+      <c r="M26" s="11" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="n"/>
@@ -4123,6 +4224,8 @@
       <c r="I27" s="11" t="n"/>
       <c r="J27" s="11" t="n"/>
       <c r="K27" s="11" t="n"/>
+      <c r="L27" s="11" t="n"/>
+      <c r="M27" s="11" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="n"/>
@@ -4136,6 +4239,8 @@
       <c r="I28" s="11" t="n"/>
       <c r="J28" s="11" t="n"/>
       <c r="K28" s="11" t="n"/>
+      <c r="L28" s="11" t="n"/>
+      <c r="M28" s="11" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="n"/>
@@ -4149,6 +4254,8 @@
       <c r="I29" s="11" t="n"/>
       <c r="J29" s="11" t="n"/>
       <c r="K29" s="11" t="n"/>
+      <c r="L29" s="11" t="n"/>
+      <c r="M29" s="11" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="n"/>
@@ -4162,6 +4269,8 @@
       <c r="I30" s="11" t="n"/>
       <c r="J30" s="11" t="n"/>
       <c r="K30" s="11" t="n"/>
+      <c r="L30" s="11" t="n"/>
+      <c r="M30" s="11" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="n"/>
@@ -4175,6 +4284,8 @@
       <c r="I31" s="11" t="n"/>
       <c r="J31" s="11" t="n"/>
       <c r="K31" s="11" t="n"/>
+      <c r="L31" s="11" t="n"/>
+      <c r="M31" s="11" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="n"/>
@@ -4188,6 +4299,8 @@
       <c r="I32" s="11" t="n"/>
       <c r="J32" s="11" t="n"/>
       <c r="K32" s="11" t="n"/>
+      <c r="L32" s="11" t="n"/>
+      <c r="M32" s="11" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="n"/>
@@ -4201,6 +4314,8 @@
       <c r="I33" s="11" t="n"/>
       <c r="J33" s="11" t="n"/>
       <c r="K33" s="11" t="n"/>
+      <c r="L33" s="11" t="n"/>
+      <c r="M33" s="11" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="n"/>
@@ -4214,6 +4329,8 @@
       <c r="I34" s="11" t="n"/>
       <c r="J34" s="11" t="n"/>
       <c r="K34" s="11" t="n"/>
+      <c r="L34" s="11" t="n"/>
+      <c r="M34" s="11" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="n"/>
@@ -4227,6 +4344,8 @@
       <c r="I35" s="11" t="n"/>
       <c r="J35" s="11" t="n"/>
       <c r="K35" s="11" t="n"/>
+      <c r="L35" s="11" t="n"/>
+      <c r="M35" s="11" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="n"/>
@@ -4240,6 +4359,8 @@
       <c r="I36" s="11" t="n"/>
       <c r="J36" s="11" t="n"/>
       <c r="K36" s="11" t="n"/>
+      <c r="L36" s="11" t="n"/>
+      <c r="M36" s="11" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="n"/>
@@ -4253,6 +4374,8 @@
       <c r="I37" s="11" t="n"/>
       <c r="J37" s="11" t="n"/>
       <c r="K37" s="11" t="n"/>
+      <c r="L37" s="11" t="n"/>
+      <c r="M37" s="11" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="n"/>
@@ -4266,6 +4389,8 @@
       <c r="I38" s="11" t="n"/>
       <c r="J38" s="11" t="n"/>
       <c r="K38" s="11" t="n"/>
+      <c r="L38" s="11" t="n"/>
+      <c r="M38" s="11" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="n"/>
@@ -4279,6 +4404,8 @@
       <c r="I39" s="11" t="n"/>
       <c r="J39" s="11" t="n"/>
       <c r="K39" s="11" t="n"/>
+      <c r="L39" s="11" t="n"/>
+      <c r="M39" s="11" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
